--- a/claude-with-tools/plots/java_cost.xlsx
+++ b/claude-with-tools/plots/java_cost.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emmayu/Desktop/llm-with-tools/claude-with-tools/plots/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{51674FDF-C7FF-8F4E-8E18-D8536A0BE9D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FB70092-00B3-E04A-B652-51D91F64B825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1500" yWindow="1320" windowWidth="27640" windowHeight="16940" activeTab="4" xr2:uid="{7CC82678-483B-024A-85B1-A6FCEC91BF8D}"/>
   </bookViews>
@@ -468,10 +468,16 @@
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B5">
+        <v>0.60436974999999904</v>
+      </c>
     </row>
     <row r="6" spans="1:2" ht="29">
       <c r="A6" s="1" t="s">
         <v>3</v>
+      </c>
+      <c r="B6">
+        <v>0.229663749999999</v>
       </c>
     </row>
   </sheetData>
@@ -501,10 +507,16 @@
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B5">
+        <v>0.47948249999999998</v>
+      </c>
     </row>
     <row r="6" spans="1:2" ht="29">
       <c r="A6" s="1" t="s">
         <v>3</v>
+      </c>
+      <c r="B6">
+        <v>0.29851100000000003</v>
       </c>
     </row>
   </sheetData>
@@ -534,10 +546,16 @@
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B5">
+        <v>0.92244524999999999</v>
+      </c>
     </row>
     <row r="6" spans="1:2" ht="29">
       <c r="A6" s="1" t="s">
         <v>3</v>
+      </c>
+      <c r="B6">
+        <v>0.43297999999999998</v>
       </c>
     </row>
   </sheetData>
@@ -567,10 +585,16 @@
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B5">
+        <v>0.392355749999999</v>
+      </c>
     </row>
     <row r="6" spans="1:2" ht="29">
       <c r="A6" s="1" t="s">
         <v>3</v>
+      </c>
+      <c r="B6">
+        <v>0.18200749999999999</v>
       </c>
     </row>
   </sheetData>
@@ -600,10 +624,16 @@
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:2" ht="29">
       <c r="A6" s="1" t="s">
         <v>3</v>
+      </c>
+      <c r="B6">
+        <v>0.29949499999999901</v>
       </c>
     </row>
   </sheetData>
